--- a/curation/draft/package18/R18_BC_SDTM_SC.xlsx
+++ b/curation/draft/package18/R18_BC_SDTM_SC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\curation\draft\package18\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D3B73F-27B6-4EB6-8385-5EECD86B502E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0877C5E8-8AD6-4FC6-A870-AC0BA615E287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{084E7D88-468F-42AF-93C9-20A71318CBFF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{084E7D88-468F-42AF-93C9-20A71318CBFF}"/>
   </bookViews>
   <sheets>
     <sheet name="BC_SC" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12933" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12933" uniqueCount="574">
   <si>
     <t>package_date</t>
   </si>
@@ -1760,9 +1760,6 @@
   </si>
   <si>
     <t>SCSTRES</t>
-  </si>
-  <si>
-    <t>FEMAL;MALE;INTERSEX;NOT REPORTED</t>
   </si>
   <si>
     <t>Type I;Type II;Type III;Type IV;Type V;Type VI</t>
@@ -10019,7 +10016,7 @@
         <v>23</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>573</v>
+        <v>478</v>
       </c>
     </row>
     <row r="186" spans="1:17" s="7" customFormat="1" ht="51.75" x14ac:dyDescent="0.25">
@@ -10268,7 +10265,7 @@
         <v>23</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="192" spans="1:17" s="7" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -50403,6 +50400,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Description0 xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">Data and Metadata documentation will explain structure and content any QC manipulations that have been done to the data.</Description0>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EA3DD6FD0640724CAC6A104AA4040E53" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="866aaee467307fab2f51bbdbaaea79d8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3dc215b4-4765-4137-95ef-e24fb8216673" xmlns:ns3="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636a025d234e12dfc0e20f1263040641" ns2:_="" ns3:_="">
     <xsd:import namespace="3dc215b4-4765-4137-95ef-e24fb8216673"/>
@@ -50659,18 +50668,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Description0 xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">Data and Metadata documentation will explain structure and content any QC manipulations that have been done to the data.</Description0>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dc215b4-4765-4137-95ef-e24fb8216673">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F44C073-52E6-4FA6-ADF0-61F510F5352C}">
   <ds:schemaRefs>
@@ -50680,6 +50677,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F93A2CBE-55C8-4891-BF09-66838DBF9DDE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3dc215b4-4765-4137-95ef-e24fb8216673"/>
+    <ds:schemaRef ds:uri="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D640222A-5E37-4D25-BB69-B194B81B2D9D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -50698,17 +50706,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F93A2CBE-55C8-4891-BF09-66838DBF9DDE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3dc215b4-4765-4137-95ef-e24fb8216673"/>
-    <ds:schemaRef ds:uri="2634c873-c79e-4fdd-b8bf-a33e5fa5c27f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{078244a1-de67-4c9e-9088-986d7f110a37}" enabled="0" method="" siteId="{078244a1-de67-4c9e-9088-986d7f110a37}" removed="1"/>
